--- a/starter_cards.xlsx
+++ b/starter_cards.xlsx
@@ -58,29 +58,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.000000"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -103,17 +86,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,46 +588,46 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="60">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="105">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="75">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
     </row>

--- a/starter_cards.xlsx
+++ b/starter_cards.xlsx
@@ -33,7 +33,7 @@
     <t>Attack</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 Damage to the Monster.</t>
+    <t xml:space="preserve">Deal 2 Damage to the Monster.</t>
   </si>
   <si>
     <t>cardimages/defend.png</t>
@@ -42,7 +42,7 @@
     <t>Defend</t>
   </si>
   <si>
-    <t xml:space="preserve">Prevent 1 Damage you would take this turn.</t>
+    <t xml:space="preserve">Prevent 2 Damage you would take this turn.</t>
   </si>
   <si>
     <t>cardimages/gather.png</t>
@@ -86,7 +86,11 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -586,6 +590,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="3" max="3" width="38.140625"/>
+  </cols>
   <sheetData>
     <row r="1" ht="15">
       <c r="A1" t="s">
@@ -630,6 +637,36 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6"/>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8"/>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9"/>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
